--- a/output/supplementary/P3_validation_infrastructure.xlsx
+++ b/output/supplementary/P3_validation_infrastructure.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9834710743801653</v>
+        <v>0.9853076216712581</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006427915518824609</v>
+        <v>0.007346189164370982</v>
       </c>
     </row>
     <row r="4">
